--- a/order_management/24.2-filters/24.2 - Filters.xlsx
+++ b/order_management/24.2-filters/24.2 - Filters.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Endpoints" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Open Questions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Cross-Epic Dependencies" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Implementation Status" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requirements'!$A$1:$K$10</definedName>
@@ -107,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -140,6 +141,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -507,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -646,6 +653,54 @@
       </c>
       <c r="B13" s="8" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Implementation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Not started — analysis only</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Impl Branch</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Impl Commits</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -659,7 +714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -673,6 +728,7 @@
     <col width="48" customWidth="1" min="9" max="9"/>
     <col width="62" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -731,6 +787,11 @@
           <t>Confluence</t>
         </is>
       </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>Impl Status (2026-07-01)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -784,6 +845,11 @@
           <t>Open §Order Management → Story 24.2</t>
         </is>
       </c>
+      <c r="L2" s="12" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -837,6 +903,11 @@
           <t>Open §Order Management → Story 24.2</t>
         </is>
       </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -888,6 +959,11 @@
       <c r="K4" s="10" t="inlineStr">
         <is>
           <t>Open §Order Management → Story 24.2</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
         </is>
       </c>
     </row>
@@ -939,6 +1015,11 @@
           <t>Open §Order Management → Story 24.2</t>
         </is>
       </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -992,6 +1073,11 @@
           <t>Open §Order Management → Story 24.2</t>
         </is>
       </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1045,6 +1131,11 @@
           <t>Open §Order Management → Story 24.2</t>
         </is>
       </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1098,6 +1189,11 @@
           <t>Open §Order Management → Story 24.2</t>
         </is>
       </c>
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1151,6 +1247,11 @@
           <t>Open §Order Management → Story 24.2</t>
         </is>
       </c>
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1202,6 +1303,11 @@
       <c r="K10" s="10" t="inlineStr">
         <is>
           <t>Open §Order Management → Story 24.2</t>
+        </is>
+      </c>
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
         </is>
       </c>
     </row>
@@ -1330,11 +1436,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="120" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1348,6 +1456,16 @@
           <t>Open Question</t>
         </is>
       </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Resolution / Decision</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -1358,6 +1476,16 @@
           <t>Sales Channel: the spec defines exactly two values (Admin Role/Sales Order, Self-Service Portal Order). There is no order-level channel column, and orders with null cart_id (subscription/ppl_addon orders, and the exhibitor payments.service product/ppl_addon path) carry no cart.created_by_type discriminator. Should such orders be excluded from the channel filter, or assigned a default channel by origin (e.g. exhibitor-backend orders -&gt; Self-Service)?</t>
         </is>
       </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>Open — for team discussion</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>Current direction (2026-07-01): (pending team confirmation). Current leaning: treat null-cart_id orders as unmatched (excluded) when a Sales Channel value is selected, since there is no reliable discriminator; an origin-based default (exhibitor-backend -&gt; Self-Service) is the fallback if the team prefers every order to carry a channel.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -1366,6 +1494,16 @@
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Show City: orders with no show linkage (subscription/ppl_addon orders, and product orders created by exhibitor payments.service which omit show_product_id) cannot be matched to a show city. When a Show City filter is applied, should these orders be excluded entirely (no city match)?</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Open — for team discussion</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>Current direction (2026-07-01): (pending team confirmation). Current leaning: exclude non-show-linked orders from the result set when a Show City filter is active (they have no derivable city), consistent with the AND semantics of the combined filters.</t>
         </is>
       </c>
     </row>
@@ -1417,4 +1555,142 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>Not started — analysis/feasibility stage only. No branch, no SBE ticket, no PR, no Swagger tag. Every in-scope requirement is (◻) Not started.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>— (not started).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Remaining — all 9 reqs</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>All in-scope requirements remain: 24.2-a (date range), 24.2-b (End&gt;=Start validation), 24.2-c (Show City filter — Partial coverage), 24.2-d (Show City dropdown), 24.2-e (Sales Channel filter — Partial coverage), 24.2-f (combinable AND), 24.2-g (empty state), 24.2-h (backend enforcement), 24.2-i (date range params).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Partial coverage — 24.2-c Show City</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Derivable only for cart-originated product orders (OrderItem -&gt; ShowProduct -&gt; Show -&gt; City). Subscription/ppl_addon orders and exhibitor payments.service product orders omit show_product_id and cannot be matched to a show city.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Partial coverage — 24.2-e Sales Channel</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Derived from cart.created_by_type (admin -&gt; Admin/Sales; exhibitor -&gt; Self-Service). Orders with null cart_id (subscription/ppl_addon and the exhibitor payments.service path) have no channel discriminator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Open decision — Sales Channel for null-cart orders</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Exclude null-cart_id orders from the channel filter, or assign a default channel by origin (exhibitor-backend -&gt; Self-Service)? No code until answered. (24.2-e)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Open decision — Show City for non-show orders</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>When a Show City filter is applied, exclude orders with no show linkage entirely? No code until answered. (24.2-c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Dependency — 24.1</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Filters are query params on the shared GET /api/v1/orders list endpoint owned by story 24.1 (also shared with 24.3, 24.4). The filter WHERE logic is 24.2 own work but rides on that endpoint. Same epic — not a cross-epic dependency (Cross-Epic Dependencies = None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Out of API scope</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Front-end wiring — the calendar picker and Custom range option (24.2-i). Nothing in this story is marked Out of Scope.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/order_management/24.2-filters/24.2 - Filters.xlsx
+++ b/order_management/24.2-filters/24.2 - Filters.xlsx
@@ -44,7 +44,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +81,24 @@
         <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+        <bgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BFBFBF"/>
+        <bgColor rgb="00BFBFBF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -108,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -147,6 +165,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -565,7 +592,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>9 requirement(s) to implement here (filter Build Focus = 'Implement here'). 0 covered elsewhere, 0 out of scope.</t>
+          <t>8 requirement(s) to implement here (filter Build Focus = 'Implement here'). 1 covered elsewhere, 0 out of scope.</t>
         </is>
       </c>
     </row>
@@ -576,7 +603,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" ht="80" customHeight="1">
@@ -612,7 +639,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -622,7 +649,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -648,11 +675,11 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Out of Scope</t>
+          <t>Delegated</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -920,9 +947,9 @@
           <t>Show City filter: returns only orders matching the selected show city; combinable with others.</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Deliverable</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -937,7 +964,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>No city column on Order. Show city is derivable only via OrderItem.show_product_id -&gt; ShowProduct.show_id -&gt; Shows.city_id -&gt; City, and show_product_id is written ONLY on cart-originated product orders (admin checkout.service and exhibitor cart.service.materializeCartToOrder). Subscription/ppl_addon orders, and product/ppl_addon orders created by exhibitor payments.service, carry no show_product_id, so they cannot be matched by Show City. The filter is buildable via a nested orderItems-&gt;showProduct-&gt;show.city_id relation filter for show-linked orders; behavior for non-show orders must be defined. billing_city is the customer billing address (and is not even populated by admin checkout), so it is not a substitute for show city.</t>
+          <t>Deliverable 2026-07-02 (exclude-unmatched). The OM list is scoped to order_type = product (per 24.1-a), so subscription/ppl_addon orders — which never carry show_product_id — are irrelevant here. Among product orders: the cart-checkout paths (admin checkout.service.ts:283; exhibitor cart.helpers.ts:55/142 materializeCartToOrder) DO write show_product_id, so they are matchable via a nested orderItems -&gt; showProduct -&gt; show.city_id relation filter. The secondary exhibitor payments.service path (payments.service.ts:217) creates product orders WITHOUT show_product_id, but those line items have no show at all — so excluding them from a Show City filter is semantically correct, not a coverage bug. Caveat to document: non-show-linked product orders never appear under a Show City filter.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -963,7 +990,7 @@
       </c>
       <c r="L4" s="12" t="inlineStr">
         <is>
-          <t>◻ Not started</t>
+          <t>Deliverable (exclude-unmatched); resolved 2026-07-02 — product-only scope, nested show.city_id relation filter.</t>
         </is>
       </c>
     </row>
@@ -978,24 +1005,24 @@
           <t>Show City dropdown options (list of cities to choose from).</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Deliverable</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Implement here</t>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Delegated</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Covered elsewhere</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>existing GET /api/v1/cities (city-management module)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>City is a real, populated model with an existing admin list endpoint (GET /cities). The dropdown sources from it, optionally narrowed to cities that have shows via City.shows. No new data needed.</t>
+          <t>Delegated to / reuses the pre-existing city-management list endpoint — nothing is built in this story for the dropdown. City is a real, populated model already served by the admin GET /api/v1/cities list endpoint; the Show City dropdown sources its options from that existing endpoint (optionally narrowed to cities that have shows via City.shows). No new endpoint and no work in this story.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1017,7 +1044,7 @@
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>◻ Not started</t>
+          <t>Delegated — reuses the existing GET /api/v1/cities (city-management); no work here.</t>
         </is>
       </c>
     </row>
@@ -1032,9 +1059,9 @@
           <t>Sales Channel filter: Admin Role/Sales Order vs Self-Service Portal Order; returns only matching orders, combinable.</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Deliverable</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1049,12 +1076,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>No order_source/sales_channel column on Order. The Admin/Sales vs Self-Service distinction can be derived from the linked cart's owner type (cart.created_by_type: admin = internal user/admin or sales -&gt; 'Admin Role/Sales Order'; exhibitor -&gt; 'Self-Service Portal Order'), filterable via a nested cart relation. But Order.cart_id is nullable and set only on cart-originated product orders; subscription/ppl_addon orders and the exhibitor payments.service product/ppl_addon path have null cart_id and thus no channel discriminator. Order.sales_person_id is sales/referral attribution (null for exhibitor owners and for non-sales admin owners), not a clean channel flag, so it cannot stand in for the filter.</t>
+          <t>Deliverable 2026-07-02. There is no order_source/sales_channel column on Order, but the Admin/Sales vs Self-Service distinction maps cleanly onto the linked cart's owner type (cart.created_by_type: admin -&gt; 'Admin Role/Sales Order'; exhibitor -&gt; 'Self-Service Portal Order'). The OM list is locked to order_type = product (per 24.1-a), and by design every product order is born from a Cart and therefore always carries a cart_id — only subscription/ppl_addon orders have null cart_id, and those are out of scope. So cart.created_by_type is always present for in-scope rows, giving a clean, total 2-way mapping with NO coverage gap, filterable via a nested cart.created_by_type condition in the composed Prisma where (same pattern as 24.2-c/-f). The Order.sales_person_id Sales-vs-non-sales-Admin nuance is only relevant to the display column (24.1-j), not to this 2-value filter.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Order.cart_id nullable admin-backend-api/prisma/schema.prisma:1576; cart_id set: checkout.service.ts:271 and exhibitor cart.service.ts:1234; cart_id NOT set: exhibitor-backend-api/src/payments/services/payments.service.ts:186-214 and exhibitor ppl/services/checkout.service.ts:169; CartOwnerType admin|exhibitor schema.prisma:2736-2741, Cart.created_by_type schema.prisma:2788; resolveSalesPersonId returns null for exhibitor and non-sales admin checkout.service.ts:355-372</t>
+          <t>CartOwnerType admin|exhibitor schema.prisma:2736-2741; Cart.created_by_type schema.prisma:2788; product-order cart_id set at admin checkout.service.ts:271 (and exhibitor cart materialization); out-of-scope note: subscription/ppl_addon orders carry null cart_id (exhibitor-backend-api/src/payments/services/payments.service.ts:186-214) but are excluded by the order_type = product scope</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -1075,7 +1102,7 @@
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>◻ Not started</t>
+          <t>Deliverable; resolved 2026-07-02 — product-only scope guarantees cart_id, cart.created_by_type maps every in-scope order to one channel (no gap).</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1505,12 @@
       </c>
       <c r="C2" s="12" t="inlineStr">
         <is>
-          <t>Open — for team discussion</t>
+          <t>RESOLVED (2026-07-02)</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>Current direction (2026-07-01): (pending team confirmation). Current leaning: treat null-cart_id orders as unmatched (excluded) when a Sales Channel value is selected, since there is no reliable discriminator; an origin-based default (exhibitor-backend -&gt; Self-Service) is the fallback if the team prefers every order to carry a channel.</t>
+          <t>Decision (2026-07-02): The OM list is scoped to order_type = product, and product orders always carry cart_id, so no null-cart orders exist in scope — the exclude-vs-default question is moot. 24.2-e is Deliverable: the filter maps cart.created_by_type admin -&gt; Admin Role/Sales Order, exhibitor -&gt; Self-Service Portal Order, with no coverage gap.</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1525,12 @@
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Open — for team discussion</t>
+          <t>RESOLVED (2026-07-02)</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Current direction (2026-07-01): (pending team confirmation). Current leaning: exclude non-show-linked orders from the result set when a Show City filter is active (they have no derivable city), consistent with the AND semantics of the combined filters.</t>
+          <t>Decision (2026-07-02): 24.2-c is Deliverable with exclude-unmatched semantics — build the nested orderItems-&gt;showProduct-&gt;show.city_id relation filter; product orders with no show linkage correctly don't match. Documented caveat: those non-show-linked product orders never appear under a Show City filter.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1641,7 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>All in-scope requirements remain: 24.2-a (date range), 24.2-b (End&gt;=Start validation), 24.2-c (Show City filter — Partial coverage), 24.2-d (Show City dropdown), 24.2-e (Sales Channel filter — Partial coverage), 24.2-f (combinable AND), 24.2-g (empty state), 24.2-h (backend enforcement), 24.2-i (date range params).</t>
+          <t>All in-scope requirements remain: 24.2-a (date range), 24.2-b (End&gt;=Start validation), 24.2-c (Show City filter — Partial coverage), 24.2-d (Show City dropdown), 24.2-e (Sales Channel filter — Deliverable), 24.2-f (combinable AND), 24.2-g (empty state), 24.2-h (backend enforcement), 24.2-i (date range params).</t>
         </is>
       </c>
     </row>
@@ -1633,24 +1660,24 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>Partial coverage — 24.2-e Sales Channel</t>
+          <t>Deliverable — 24.2-e Sales Channel</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Derived from cart.created_by_type (admin -&gt; Admin/Sales; exhibitor -&gt; Self-Service). Orders with null cart_id (subscription/ppl_addon and the exhibitor payments.service path) have no channel discriminator.</t>
+          <t>Derived from cart.created_by_type (admin -&gt; Admin Role/Sales Order; exhibitor -&gt; Self-Service Portal Order). The product-only scope guarantees every in-scope order carries a cart_id (only subscription/ppl_addon have null cart_id, and those are out of scope), so every in-scope order resolves to exactly one channel — no coverage gap. (resolved 2026-07-02)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>Open decision — Sales Channel for null-cart orders</t>
+          <t>Resolved decision — Sales Channel for null-cart orders</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Exclude null-cart_id orders from the channel filter, or assign a default channel by origin (exhibitor-backend -&gt; Self-Service)? No code until answered. (24.2-e)</t>
+          <t>RESOLVED 2026-07-02: moot in scope. The OM list is scoped to order_type = product, and product orders always carry cart_id, so no null-cart orders exist in scope; 24.2-e is Deliverable, mapping cart.created_by_type admin -&gt; Admin Role/Sales Order, exhibitor -&gt; Self-Service Portal Order. (24.2-e)</t>
         </is>
       </c>
     </row>

--- a/order_management/24.2-filters/24.2 - Filters.xlsx
+++ b/order_management/24.2-filters/24.2 - Filters.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,8 +43,12 @@
       <color rgb="000563C1"/>
       <u val="single"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -99,8 +103,13 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -122,11 +131,25 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -175,6 +198,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -690,7 +722,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Not started — analysis only</t>
+          <t>All 8 implement-here reqs shipped in SBE-1125 (GET /api/v1/orders filters); 24.2-d Delegated → GET /api/v1/cities</t>
         </is>
       </c>
     </row>
@@ -702,7 +734,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SBE-1125 (admin-backend-api)</t>
         </is>
       </c>
     </row>
@@ -714,7 +746,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6dc3104 (feat — OM list endpoint), b95627b (SonarQube S7781 fix)</t>
         </is>
       </c>
     </row>
@@ -726,7 +758,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bitbucket #513 → dev</t>
         </is>
       </c>
     </row>
@@ -816,7 +848,7 @@
       </c>
       <c r="L1" s="9" t="inlineStr">
         <is>
-          <t>Impl Status (2026-07-01)</t>
+          <t>Impl Status (2026-07-02)</t>
         </is>
       </c>
     </row>
@@ -872,9 +904,9 @@
           <t>Open §Order Management → Story 24.2</t>
         </is>
       </c>
-      <c r="L2" s="12" t="inlineStr">
-        <is>
-          <t>◻ Not started</t>
+      <c r="L2" s="17" t="inlineStr">
+        <is>
+          <t>✅ Done — from_date/to_date → created_at gte/lte.</t>
         </is>
       </c>
     </row>
@@ -930,9 +962,9 @@
           <t>Open §Order Management → Story 24.2</t>
         </is>
       </c>
-      <c r="L3" s="12" t="inlineStr">
-        <is>
-          <t>◻ Not started</t>
+      <c r="L3" s="17" t="inlineStr">
+        <is>
+          <t>✅ Done — from≤to guard (+ calendar-validity: rejects e.g. 2026-02-30).</t>
         </is>
       </c>
     </row>
@@ -988,9 +1020,9 @@
           <t>Open §Order Management → Story 24.2</t>
         </is>
       </c>
-      <c r="L4" s="12" t="inlineStr">
-        <is>
-          <t>Deliverable (exclude-unmatched); resolved 2026-07-02 — product-only scope, nested show.city_id relation filter.</t>
+      <c r="L4" s="17" t="inlineStr">
+        <is>
+          <t>✅ Done — show_city_id nested orderItems→showProduct→show.city_id (exclude-unmatched).</t>
         </is>
       </c>
     </row>
@@ -1042,9 +1074,9 @@
           <t>Open §Order Management → Story 24.2</t>
         </is>
       </c>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>Delegated — reuses the existing GET /api/v1/cities (city-management); no work here.</t>
+      <c r="L5" s="17" t="inlineStr">
+        <is>
+          <t>Delegated → GET /api/v1/cities (city-management); no work here.</t>
         </is>
       </c>
     </row>
@@ -1100,9 +1132,9 @@
           <t>Open §Order Management → Story 24.2</t>
         </is>
       </c>
-      <c r="L6" s="12" t="inlineStr">
-        <is>
-          <t>Deliverable; resolved 2026-07-02 — product-only scope guarantees cart_id, cart.created_by_type maps every in-scope order to one channel (no gap).</t>
+      <c r="L6" s="17" t="inlineStr">
+        <is>
+          <t>✅ Done — sales_channel from cart.created_by_type (exhibitor→self_service, else admin_sales).</t>
         </is>
       </c>
     </row>
@@ -1158,9 +1190,9 @@
           <t>Open §Order Management → Story 24.2</t>
         </is>
       </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>◻ Not started</t>
+      <c r="L7" s="17" t="inlineStr">
+        <is>
+          <t>✅ Done — filters AND-composed into a single Prisma where.</t>
         </is>
       </c>
     </row>
@@ -1216,9 +1248,9 @@
           <t>Open §Order Management → Story 24.2</t>
         </is>
       </c>
-      <c r="L8" s="12" t="inlineStr">
-        <is>
-          <t>◻ Not started</t>
+      <c r="L8" s="17" t="inlineStr">
+        <is>
+          <t>✅ Done — empty paginated result (totalPages 0) on no match.</t>
         </is>
       </c>
     </row>
@@ -1274,9 +1306,9 @@
           <t>Open §Order Management → Story 24.2</t>
         </is>
       </c>
-      <c r="L9" s="12" t="inlineStr">
-        <is>
-          <t>◻ Not started</t>
+      <c r="L9" s="17" t="inlineStr">
+        <is>
+          <t>✅ Done — server-side Prisma where on the Order table.</t>
         </is>
       </c>
     </row>
@@ -1332,9 +1364,9 @@
           <t>Open §Order Management → Story 24.2</t>
         </is>
       </c>
-      <c r="L10" s="12" t="inlineStr">
-        <is>
-          <t>◻ Not started</t>
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <t>✅ Done — backend accepts arbitrary from/to (calendar picker is FE).</t>
         </is>
       </c>
     </row>
@@ -1590,130 +1622,166 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="18" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
-        <is>
-          <t>Not started — analysis/feasibility stage only. No branch, no SBE ticket, no PR, no Swagger tag. Every in-scope requirement is (◻) Not started.</t>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>Shipped — built, live-smoke-tested, code-reviewed; all gates green; PR open against dev (not yet merged).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>— (not started).</t>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>SBE-1125 (admin-backend-api)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Remaining — all 9 reqs</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>All in-scope requirements remain: 24.2-a (date range), 24.2-b (End&gt;=Start validation), 24.2-c (Show City filter — Partial coverage), 24.2-d (Show City dropdown), 24.2-e (Sales Channel filter — Deliverable), 24.2-f (combinable AND), 24.2-g (empty state), 24.2-h (backend enforcement), 24.2-i (date range params).</t>
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>SBE ticket</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>SBE-1125</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Partial coverage — 24.2-c Show City</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Derivable only for cart-originated product orders (OrderItem -&gt; ShowProduct -&gt; Show -&gt; City). Subscription/ppl_addon orders and exhibitor payments.service product orders omit show_product_id and cannot be matched to a show city.</t>
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>Commits</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>6dc3104 (feat — OM list endpoint), b95627b (SonarQube S7781 fix)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Deliverable — 24.2-e Sales Channel</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Derived from cart.created_by_type (admin -&gt; Admin Role/Sales Order; exhibitor -&gt; Self-Service Portal Order). The product-only scope guarantees every in-scope order carries a cart_id (only subscription/ppl_addon have null cart_id, and those are out of scope), so every in-scope order resolves to exactly one channel — no coverage gap. (resolved 2026-07-02)</t>
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Bitbucket #513 → dev</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Resolved decision — Sales Channel for null-cart orders</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>RESOLVED 2026-07-02: moot in scope. The OM list is scoped to order_type = product, and product orders always carry cart_id, so no null-cart orders exist in scope; 24.2-e is Deliverable, mapping cart.created_by_type admin -&gt; Admin Role/Sales Order, exhibitor -&gt; Self-Service Portal Order. (24.2-e)</t>
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>Swagger tag</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Admin - Order Management (/api/docs/admin)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Open decision — Show City for non-show orders</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>When a Show City filter is applied, exclude orders with no show linkage entirely? No code until answered. (24.2-c)</t>
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>Build gates</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>Pipeline #838 SUCCESSFUL — gitleaks + lint/typecheck/test (2702 pass; orders module 48) + SonarQube quality gate all green</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Dependency — 24.1</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Filters are query params on the shared GET /api/v1/orders list endpoint owned by story 24.1 (also shared with 24.3, 24.4). The filter WHERE logic is 24.2 own work but rides on that endpoint. Same epic — not a cross-epic dependency (Cross-Epic Dependencies = None).</t>
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>Live smoke</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Filter matrix + seeded fixture: self_service/admin_sales partitioning incl. null-cart orders, calendar-invalid dates → 400, combinable filters — all passed</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>Confirmed build scope</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>GET /api/v1/orders query params — 24.2-a,b,c,e,f,g,h,i shipped (all 8 implement-here). from_date/to_date (calendar-validated, End≥Start), show_city_id (nested show.city_id), sales_channel (cart.created_by_type); AND-combinable; empty state = empty page (totalPages 0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>Delegated — 24.2-d</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>Show City dropdown → existing GET /api/v1/cities (city-management); no work in this story.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>None — all 8 implement-here requirements shipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Out of API scope</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>Front-end wiring — the calendar picker and Custom range option (24.2-i). Nothing in this story is marked Out of Scope.</t>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>Front-end calendar picker + 'Custom' range option (24.2-i).</t>
         </is>
       </c>
     </row>
